--- a/excess_sensitivity/studies.xlsx
+++ b/excess_sensitivity/studies.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="19226"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Study\Papers\24_Excess_Sensitivity\web\excess_sensitivity\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="10_ncr:8100000_{2794CDE9-3DB4-4E10-A5AE-BB8AEA4714F0}" xr6:coauthVersionLast="32" xr6:coauthVersionMax="32" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="480" yWindow="120" windowWidth="20730" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
@@ -5639,6 +5634,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
 </worksheet>
 </file>